--- a/research/fasih-dashboard-se2026/8Juli2026/Agregat_PCL_ANGGOTA KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/8Juli2026/Agregat_PCL_ANGGOTA KELUARGA.xlsx
@@ -701,13 +701,13 @@
         <v>161</v>
       </c>
       <c r="O2" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="P2" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -731,16 +731,16 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z2" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AA2" t="n">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AB2" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -767,10 +767,10 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL2" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AM2" t="n">
         <v>384</v>
@@ -844,19 +844,19 @@
         <v>214</v>
       </c>
       <c r="O3" t="n">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="P3" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -868,31 +868,31 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Z3" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="AA3" t="n">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="AB3" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -904,16 +904,16 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL3" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="AM3" t="n">
         <v>354</v>
@@ -987,10 +987,10 @@
         <v>359</v>
       </c>
       <c r="O4" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="P4" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1011,31 +1011,31 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="Z4" t="n">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="AA4" t="n">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="AB4" t="n">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AL4" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="AM4" t="n">
         <v>336</v>
@@ -1130,13 +1130,13 @@
         <v>367</v>
       </c>
       <c r="O5" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="P5" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1160,19 +1160,19 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Z5" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AA5" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1196,10 +1196,10 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL5" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AM5" t="n">
         <v>288</v>
@@ -1273,22 +1273,22 @@
         <v>220</v>
       </c>
       <c r="O6" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="P6" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1303,28 +1303,28 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="Z6" t="n">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="AA6" t="n">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="AB6" t="n">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="AC6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1339,10 +1339,10 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AL6" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="AM6" t="n">
         <v>303</v>
@@ -1551,19 +1551,19 @@
         <v>259</v>
       </c>
       <c r="O8" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P8" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1575,31 +1575,31 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Z8" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AA8" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AB8" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="AC8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL8" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM8" t="n">
         <v>324</v>
@@ -1697,19 +1697,19 @@
         <v>238</v>
       </c>
       <c r="P9" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1724,28 +1724,28 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z9" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AA9" t="n">
         <v>238</v>
       </c>
       <c r="AB9" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="AC9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1760,10 +1760,10 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL9" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AM9" t="n">
         <v>379</v>
@@ -1837,19 +1837,19 @@
         <v>300</v>
       </c>
       <c r="O10" t="n">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="P10" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1867,25 +1867,25 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Z10" t="n">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="AA10" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AB10" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL10" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AM10" t="n">
         <v>373</v>
@@ -1980,13 +1980,13 @@
         <v>301</v>
       </c>
       <c r="O11" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="P11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2004,25 +2004,25 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z11" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="AA11" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AB11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="AC11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2049,7 +2049,7 @@
         <v>435</v>
       </c>
       <c r="AL11" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AM11" t="n">
         <v>383</v>
@@ -2123,16 +2123,16 @@
         <v>388</v>
       </c>
       <c r="O12" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="P12" t="n">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2153,25 +2153,25 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="Z12" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="AA12" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="AB12" t="n">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="AL12" t="n">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="AM12" t="n">
         <v>373</v>
@@ -2266,19 +2266,19 @@
         <v>277</v>
       </c>
       <c r="O13" t="n">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="P13" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -2290,31 +2290,31 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Z13" t="n">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="AA13" t="n">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="AB13" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2326,16 +2326,16 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL13" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="AM13" t="n">
         <v>364</v>
@@ -2409,19 +2409,19 @@
         <v>301</v>
       </c>
       <c r="O14" t="n">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="Q14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2439,25 +2439,25 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z14" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="AA14" t="n">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="AB14" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="AC14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL14" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="AM14" t="n">
         <v>359</v>
@@ -2552,16 +2552,16 @@
         <v>215</v>
       </c>
       <c r="O15" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="P15" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2585,19 +2585,19 @@
         <v>398</v>
       </c>
       <c r="Z15" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AA15" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="AB15" t="n">
         <v>161</v>
       </c>
       <c r="AC15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>398</v>
       </c>
       <c r="AL15" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AM15" t="n">
         <v>367</v>
@@ -2695,22 +2695,22 @@
         <v>338</v>
       </c>
       <c r="O16" t="n">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="P16" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2719,34 +2719,34 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="Z16" t="n">
+        <v>246</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>192</v>
+      </c>
+      <c r="AB16" t="n">
         <v>226</v>
       </c>
-      <c r="AA16" t="n">
-        <v>213</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>215</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -2755,16 +2755,16 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AL16" t="n">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="AM16" t="n">
         <v>370</v>
@@ -2838,19 +2838,19 @@
         <v>279</v>
       </c>
       <c r="O17" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="P17" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="Q17" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="R17" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -2868,25 +2868,25 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="Z17" t="n">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="AA17" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="AB17" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="AC17" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2904,10 +2904,10 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AL17" t="n">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="AM17" t="n">
         <v>366</v>
@@ -2981,16 +2981,16 @@
         <v>273</v>
       </c>
       <c r="O18" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="P18" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3005,25 +3005,25 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Z18" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="AA18" t="n">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="AB18" t="n">
         <v>170</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3041,16 +3041,16 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL18" t="n">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="AM18" t="n">
         <v>423</v>
@@ -3124,16 +3124,16 @@
         <v>449</v>
       </c>
       <c r="O19" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="P19" t="n">
         <v>227</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3148,28 +3148,28 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="Z19" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AA19" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AB19" t="n">
         <v>227</v>
       </c>
       <c r="AC19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3184,16 +3184,16 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="AL19" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AM19" t="n">
         <v>371</v>
@@ -3267,13 +3267,13 @@
         <v>504</v>
       </c>
       <c r="O20" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="P20" t="n">
         <v>217</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -3300,16 +3300,16 @@
         <v>298</v>
       </c>
       <c r="Z20" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="AA20" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AB20" t="n">
         <v>217</v>
       </c>
       <c r="AC20" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
         <v>298</v>
       </c>
       <c r="AL20" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AM20" t="n">
         <v>284</v>
@@ -3410,13 +3410,13 @@
         <v>209</v>
       </c>
       <c r="O21" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="P21" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -3443,16 +3443,16 @@
         <v>401</v>
       </c>
       <c r="Z21" t="n">
+        <v>181</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB21" t="n">
         <v>177</v>
       </c>
-      <c r="AA21" t="n">
-        <v>224</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>165</v>
-      </c>
       <c r="AC21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3461,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v>401</v>
       </c>
       <c r="AL21" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AM21" t="n">
         <v>367</v>
@@ -3553,19 +3553,19 @@
         <v>241</v>
       </c>
       <c r="O22" t="n">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="P22" t="n">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="Q22" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -3583,25 +3583,25 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="Z22" t="n">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="AA22" t="n">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="AB22" t="n">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="AC22" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3619,10 +3619,10 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="AL22" t="n">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="AM22" t="n">
         <v>450</v>
@@ -3696,19 +3696,19 @@
         <v>298</v>
       </c>
       <c r="O23" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="P23" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -3726,25 +3726,25 @@
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Z23" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="AA23" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="AB23" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="AC23" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3762,10 +3762,10 @@
         <v>1</v>
       </c>
       <c r="AK23" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AL23" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="AM23" t="n">
         <v>308</v>
@@ -3839,19 +3839,19 @@
         <v>341</v>
       </c>
       <c r="O24" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="P24" t="n">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -3869,26 +3869,26 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="Z24" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="AA24" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="AB24" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AC24" t="n">
         <v>25</v>
       </c>
       <c r="AD24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE24" t="n">
         <v>3</v>
       </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
@@ -3905,10 +3905,10 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="AL24" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="AM24" t="n">
         <v>386</v>
@@ -3982,19 +3982,19 @@
         <v>135</v>
       </c>
       <c r="O25" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="P25" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="S25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -4012,25 +4012,25 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z25" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AA25" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="AB25" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AE25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -4048,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL25" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AM25" t="n">
         <v>396</v>
@@ -4125,19 +4125,19 @@
         <v>328</v>
       </c>
       <c r="O26" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="P26" t="n">
         <v>170</v>
       </c>
       <c r="Q26" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -4155,25 +4155,25 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z26" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="AA26" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="AB26" t="n">
         <v>170</v>
       </c>
       <c r="AC26" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL26" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="AM26" t="n">
         <v>282</v>
@@ -4268,13 +4268,13 @@
         <v>268</v>
       </c>
       <c r="O27" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="P27" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -4298,19 +4298,19 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Z27" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="AA27" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="AB27" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="AC27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4334,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AL27" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="AM27" t="n">
         <v>363</v>
@@ -4411,19 +4411,19 @@
         <v>256</v>
       </c>
       <c r="O28" t="n">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="P28" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -4435,31 +4435,31 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="Z28" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="AA28" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AB28" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4471,16 +4471,16 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AL28" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="AM28" t="n">
         <v>384</v>
@@ -4554,19 +4554,19 @@
         <v>311</v>
       </c>
       <c r="O29" t="n">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="P29" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -4584,16 +4584,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="Z29" t="n">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="AA29" t="n">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="AB29" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4620,10 +4620,10 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AL29" t="n">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="AM29" t="n">
         <v>357</v>
@@ -4700,13 +4700,13 @@
         <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -4727,22 +4727,22 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z30" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AA30" t="n">
         <v>10</v>
       </c>
       <c r="AB30" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4763,10 +4763,10 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL30" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AM30" t="n">
         <v>315</v>
@@ -4840,13 +4840,13 @@
         <v>316</v>
       </c>
       <c r="O31" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="P31" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4870,19 +4870,19 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Z31" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="AA31" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="AB31" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="AC31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4906,10 +4906,10 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AL31" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="AM31" t="n">
         <v>366</v>
@@ -4983,19 +4983,19 @@
         <v>272</v>
       </c>
       <c r="O32" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P32" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -5007,31 +5007,31 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="X32" t="n">
         <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="Z32" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AA32" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AB32" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -5043,16 +5043,16 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AJ32" t="n">
         <v>1</v>
       </c>
       <c r="AK32" t="n">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AL32" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AM32" t="n">
         <v>455</v>
@@ -5269,13 +5269,13 @@
         <v>220</v>
       </c>
       <c r="O34" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="P34" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -5293,22 +5293,22 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Z34" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AA34" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AB34" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5329,16 +5329,16 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK34" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AL34" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AM34" t="n">
         <v>290</v>
@@ -5412,22 +5412,22 @@
         <v>231</v>
       </c>
       <c r="O35" t="n">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="P35" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -5442,22 +5442,22 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="Z35" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="AA35" t="n">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="AB35" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="AC35" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="AD35" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -5478,10 +5478,10 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AL35" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="AM35" t="n">
         <v>372</v>
@@ -5555,13 +5555,13 @@
         <v>348</v>
       </c>
       <c r="O36" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="P36" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
         <v>2</v>
@@ -5588,16 +5588,16 @@
         <v>491</v>
       </c>
       <c r="Z36" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AA36" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="AB36" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD36" t="n">
         <v>2</v>
@@ -5624,7 +5624,7 @@
         <v>491</v>
       </c>
       <c r="AL36" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AM36" t="n">
         <v>453</v>
@@ -5698,19 +5698,19 @@
         <v>221</v>
       </c>
       <c r="O37" t="n">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="P37" t="n">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S37" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -5728,26 +5728,26 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Z37" t="n">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="AA37" t="n">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="AB37" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="AC37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE37" t="n">
         <v>18</v>
       </c>
-      <c r="AD37" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>25</v>
-      </c>
       <c r="AF37" t="n">
         <v>0</v>
       </c>
@@ -5764,10 +5764,10 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AL37" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="AM37" t="n">
         <v>445</v>
@@ -5841,19 +5841,19 @@
         <v>341</v>
       </c>
       <c r="O38" t="n">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="P38" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -5871,19 +5871,19 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z38" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AA38" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AB38" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AC38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5907,10 +5907,10 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL38" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM38" t="n">
         <v>379</v>
@@ -5984,19 +5984,19 @@
         <v>163</v>
       </c>
       <c r="O39" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="P39" t="n">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -6008,31 +6008,31 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="Z39" t="n">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="AA39" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="AB39" t="n">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="AC39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AD39" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -6044,16 +6044,16 @@
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ39" t="n">
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AL39" t="n">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="AM39" t="n">
         <v>410</v>
@@ -6127,16 +6127,16 @@
         <v>344</v>
       </c>
       <c r="O40" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="P40" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -6160,19 +6160,19 @@
         <v>395</v>
       </c>
       <c r="Z40" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="AA40" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="AB40" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6196,7 +6196,7 @@
         <v>395</v>
       </c>
       <c r="AL40" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="AM40" t="n">
         <v>378</v>
@@ -6270,19 +6270,19 @@
         <v>365</v>
       </c>
       <c r="O41" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="P41" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -6300,25 +6300,25 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z41" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AA41" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AB41" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AC41" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -6336,10 +6336,10 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL41" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AM41" t="n">
         <v>331</v>
@@ -6413,19 +6413,19 @@
         <v>289</v>
       </c>
       <c r="O42" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="P42" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -6443,25 +6443,25 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Z42" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="AA42" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="AB42" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="AC42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -6479,10 +6479,10 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AL42" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="AM42" t="n">
         <v>301</v>
@@ -6556,16 +6556,16 @@
         <v>279</v>
       </c>
       <c r="O43" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P43" t="n">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -6586,22 +6586,22 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="Z43" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="AA43" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AB43" t="n">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="AC43" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AD43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -6622,10 +6622,10 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AL43" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="AM43" t="n">
         <v>371</v>
@@ -6699,10 +6699,10 @@
         <v>194</v>
       </c>
       <c r="O44" t="n">
-        <v>277</v>
+        <v>545</v>
       </c>
       <c r="P44" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
@@ -6714,7 +6714,7 @@
         <v>15</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6723,13 +6723,13 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>385</v>
+        <v>653</v>
       </c>
       <c r="Z44" t="n">
         <v>102</v>
@@ -6738,7 +6738,7 @@
         <v>277</v>
       </c>
       <c r="AB44" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC44" t="n">
         <v>1</v>
@@ -6750,7 +6750,7 @@
         <v>15</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -6759,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
         <v>0</v>
@@ -6842,31 +6842,31 @@
         <v>325</v>
       </c>
       <c r="O45" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="P45" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="Q45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -6875,34 +6875,34 @@
         <v>461</v>
       </c>
       <c r="Z45" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="AA45" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="AB45" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="AC45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AE45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH45" t="n">
         <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ45" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
         <v>461</v>
       </c>
       <c r="AL45" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="AM45" t="n">
         <v>434</v>
@@ -6985,16 +6985,16 @@
         <v>262</v>
       </c>
       <c r="O46" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="P46" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -7018,19 +7018,19 @@
         <v>400</v>
       </c>
       <c r="Z46" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AA46" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="AB46" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="AC46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD46" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7054,7 +7054,7 @@
         <v>400</v>
       </c>
       <c r="AL46" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AM46" t="n">
         <v>375</v>
@@ -7128,13 +7128,13 @@
         <v>232</v>
       </c>
       <c r="O47" t="n">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="P47" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -7161,16 +7161,16 @@
         <v>449</v>
       </c>
       <c r="Z47" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="AA47" t="n">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="AB47" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="AC47" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -7197,7 +7197,7 @@
         <v>449</v>
       </c>
       <c r="AL47" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="AM47" t="n">
         <v>411</v>
@@ -7271,16 +7271,16 @@
         <v>226</v>
       </c>
       <c r="O48" t="n">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="P48" t="n">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -7301,22 +7301,22 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Z48" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="AA48" t="n">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="AB48" t="n">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="AC48" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -7337,10 +7337,10 @@
         <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AL48" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="AM48" t="n">
         <v>363</v>
@@ -7414,19 +7414,19 @@
         <v>286</v>
       </c>
       <c r="O49" t="n">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="P49" t="n">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
@@ -7444,25 +7444,25 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="Z49" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AA49" t="n">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="AB49" t="n">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="AC49" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -7480,10 +7480,10 @@
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AL49" t="n">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="AM49" t="n">
         <v>356</v>
@@ -7557,13 +7557,13 @@
         <v>308</v>
       </c>
       <c r="O50" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="P50" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -7575,31 +7575,31 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="Z50" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AA50" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AB50" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="AC50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7611,7 +7611,7 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH50" t="n">
         <v>0</v>
@@ -7623,10 +7623,10 @@
         <v>1</v>
       </c>
       <c r="AK50" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AL50" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AM50" t="n">
         <v>372</v>
@@ -7700,19 +7700,19 @@
         <v>325</v>
       </c>
       <c r="O51" t="n">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="P51" t="n">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -7730,25 +7730,25 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="Z51" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="AA51" t="n">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="AB51" t="n">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="AC51" t="n">
         <v>1</v>
       </c>
       <c r="AD51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AE51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AL51" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="AM51" t="n">
         <v>395</v>
@@ -7843,19 +7843,19 @@
         <v>364</v>
       </c>
       <c r="O52" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="P52" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -7867,31 +7867,31 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Z52" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="AA52" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="AB52" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="AC52" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7903,16 +7903,16 @@
         <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ52" t="n">
         <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AL52" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="AM52" t="n">
         <v>378</v>
@@ -7986,19 +7986,19 @@
         <v>325</v>
       </c>
       <c r="O53" t="n">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="P53" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
@@ -8016,25 +8016,25 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="Z53" t="n">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="AA53" t="n">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="AB53" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AF53" t="n">
         <v>0</v>
@@ -8052,10 +8052,10 @@
         <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="AL53" t="n">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="AM53" t="n">
         <v>507</v>
@@ -8129,19 +8129,19 @@
         <v>335</v>
       </c>
       <c r="O54" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="P54" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="Q54" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
         <v>0</v>
@@ -8159,25 +8159,25 @@
         <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="Z54" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="AA54" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AB54" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="AC54" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
         <v>0</v>
@@ -8195,10 +8195,10 @@
         <v>1</v>
       </c>
       <c r="AK54" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AL54" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="AM54" t="n">
         <v>407</v>
@@ -8272,13 +8272,13 @@
         <v>300</v>
       </c>
       <c r="O55" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P55" t="n">
         <v>156</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -8302,19 +8302,19 @@
         <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="Z55" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="AA55" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AB55" t="n">
         <v>156</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>1</v>
       </c>
       <c r="AK55" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AL55" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="AM55" t="n">
         <v>308</v>
@@ -8415,13 +8415,13 @@
         <v>220</v>
       </c>
       <c r="O56" t="n">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="P56" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -8445,28 +8445,28 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="Z56" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="AA56" t="n">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="AB56" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -8481,10 +8481,10 @@
         <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AL56" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="AM56" t="n">
         <v>363</v>
@@ -8558,16 +8558,16 @@
         <v>322</v>
       </c>
       <c r="O57" t="n">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="P57" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="R57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -8588,22 +8588,22 @@
         <v>1</v>
       </c>
       <c r="Y57" t="n">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="Z57" t="n">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="AA57" t="n">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="AB57" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="AC57" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AD57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -8624,10 +8624,10 @@
         <v>1</v>
       </c>
       <c r="AK57" t="n">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="AL57" t="n">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="AM57" t="n">
         <v>383</v>
@@ -8701,16 +8701,16 @@
         <v>450</v>
       </c>
       <c r="O58" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="P58" t="n">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="Q58" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S58" t="n">
         <v>7</v>
@@ -8725,31 +8725,31 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="X58" t="n">
         <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="Z58" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AA58" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AB58" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="AC58" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AD58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -8761,16 +8761,16 @@
         <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AJ58" t="n">
         <v>1</v>
       </c>
       <c r="AK58" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AL58" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AM58" t="n">
         <v>419</v>
@@ -8844,16 +8844,16 @@
         <v>262</v>
       </c>
       <c r="O59" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="P59" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="Q59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -8874,22 +8874,22 @@
         <v>1</v>
       </c>
       <c r="Y59" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Z59" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="AA59" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="AB59" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -8910,10 +8910,10 @@
         <v>1</v>
       </c>
       <c r="AK59" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AL59" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="AM59" t="n">
         <v>314</v>
@@ -8987,19 +8987,19 @@
         <v>358</v>
       </c>
       <c r="O60" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="P60" t="n">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
@@ -9017,25 +9017,25 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="Z60" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="AA60" t="n">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="AB60" t="n">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="AC60" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF60" t="n">
         <v>0</v>
@@ -9053,10 +9053,10 @@
         <v>0</v>
       </c>
       <c r="AK60" t="n">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="AL60" t="n">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="AM60" t="n">
         <v>365</v>
@@ -9130,19 +9130,19 @@
         <v>208</v>
       </c>
       <c r="O61" t="n">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="P61" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -9160,25 +9160,25 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z61" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="AA61" t="n">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="AB61" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="AC61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AD61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE61" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
@@ -9196,10 +9196,10 @@
         <v>0</v>
       </c>
       <c r="AK61" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL61" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="AM61" t="n">
         <v>365</v>
@@ -9273,16 +9273,16 @@
         <v>245</v>
       </c>
       <c r="O62" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="P62" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="Q62" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -9303,22 +9303,22 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="Z62" t="n">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="AA62" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AB62" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="AC62" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="AD62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -9339,10 +9339,10 @@
         <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="AL62" t="n">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="AM62" t="n">
         <v>405</v>
@@ -9416,13 +9416,13 @@
         <v>352</v>
       </c>
       <c r="O63" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="P63" t="n">
         <v>191</v>
       </c>
       <c r="Q63" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -9446,19 +9446,19 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="Z63" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="AA63" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AB63" t="n">
         <v>191</v>
       </c>
       <c r="AC63" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AL63" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM63" t="n">
         <v>417</v>
@@ -9559,19 +9559,19 @@
         <v>435</v>
       </c>
       <c r="O64" t="n">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="P64" t="n">
         <v>164</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
         <v>0</v>
@@ -9589,19 +9589,19 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Z64" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="AA64" t="n">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="AB64" t="n">
         <v>164</v>
       </c>
       <c r="AC64" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -9625,10 +9625,10 @@
         <v>0</v>
       </c>
       <c r="AK64" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL64" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="AM64" t="n">
         <v>303</v>
@@ -9702,22 +9702,22 @@
         <v>329</v>
       </c>
       <c r="O65" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="P65" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -9732,28 +9732,28 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z65" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AA65" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="AB65" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="AC65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -9768,10 +9768,10 @@
         <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL65" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AM65" t="n">
         <v>373</v>
@@ -9845,16 +9845,16 @@
         <v>180</v>
       </c>
       <c r="O66" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P66" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="Q66" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -9875,22 +9875,22 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Z66" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="AA66" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AB66" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="AC66" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AD66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -9911,10 +9911,10 @@
         <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL66" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="AM66" t="n">
         <v>317</v>
@@ -10131,19 +10131,19 @@
         <v>157</v>
       </c>
       <c r="O68" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="P68" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
         <v>0</v>
@@ -10161,25 +10161,25 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Z68" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="AA68" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="AB68" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="AC68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
         <v>0</v>
@@ -10197,10 +10197,10 @@
         <v>0</v>
       </c>
       <c r="AK68" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AL68" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="AM68" t="n">
         <v>278</v>
@@ -10277,16 +10277,16 @@
         <v>239</v>
       </c>
       <c r="P69" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
         <v>0</v>
@@ -10298,7 +10298,7 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X69" t="n">
         <v>1</v>
@@ -10313,16 +10313,16 @@
         <v>239</v>
       </c>
       <c r="AB69" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="AC69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
         <v>0</v>
@@ -10334,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ69" t="n">
         <v>1</v>
@@ -10417,19 +10417,19 @@
         <v>195</v>
       </c>
       <c r="O70" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="P70" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
@@ -10447,25 +10447,25 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Z70" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="AA70" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AB70" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AC70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
         <v>0</v>
@@ -10483,10 +10483,10 @@
         <v>0</v>
       </c>
       <c r="AK70" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AL70" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="AM70" t="n">
         <v>359</v>
@@ -10560,19 +10560,19 @@
         <v>282</v>
       </c>
       <c r="O71" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="P71" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="Q71" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
@@ -10590,25 +10590,25 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Z71" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="AA71" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AB71" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="AC71" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF71" t="n">
         <v>0</v>
@@ -10626,10 +10626,10 @@
         <v>0</v>
       </c>
       <c r="AK71" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL71" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AM71" t="n">
         <v>357</v>
@@ -10703,13 +10703,13 @@
         <v>326</v>
       </c>
       <c r="O72" t="n">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="P72" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="Q72" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -10733,25 +10733,25 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="Z72" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="AA72" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="AB72" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="AC72" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF72" t="n">
         <v>0</v>
@@ -10769,10 +10769,10 @@
         <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AL72" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AM72" t="n">
         <v>319</v>
@@ -10846,19 +10846,19 @@
         <v>332</v>
       </c>
       <c r="O73" t="n">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="P73" t="n">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="Q73" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T73" t="n">
         <v>0</v>
@@ -10876,25 +10876,25 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="Z73" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="AA73" t="n">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="AB73" t="n">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="AC73" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF73" t="n">
         <v>0</v>
@@ -10912,10 +10912,10 @@
         <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AL73" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="AM73" t="n">
         <v>350</v>
@@ -10989,16 +10989,16 @@
         <v>379</v>
       </c>
       <c r="O74" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="P74" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="Q74" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -11019,22 +11019,22 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="Z74" t="n">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="AA74" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="AB74" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="AC74" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE74" t="n">
         <v>0</v>
@@ -11055,10 +11055,10 @@
         <v>0</v>
       </c>
       <c r="AK74" t="n">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="AL74" t="n">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="AM74" t="n">
         <v>395</v>
@@ -11132,25 +11132,25 @@
         <v>146</v>
       </c>
       <c r="O75" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="P75" t="n">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="Q75" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
         <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -11162,31 +11162,31 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Z75" t="n">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="AA75" t="n">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="AB75" t="n">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="AC75" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
         <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="n">
         <v>0</v>
@@ -11198,10 +11198,10 @@
         <v>0</v>
       </c>
       <c r="AK75" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL75" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="AM75" t="n">
         <v>263</v>
@@ -11275,25 +11275,25 @@
         <v>301</v>
       </c>
       <c r="O76" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="P76" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="Q76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T76" t="n">
         <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -11305,31 +11305,31 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Z76" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AA76" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AB76" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AC76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF76" t="n">
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
         <v>0</v>
@@ -11341,10 +11341,10 @@
         <v>0</v>
       </c>
       <c r="AK76" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AL76" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AM76" t="n">
         <v>342</v>
@@ -11418,10 +11418,10 @@
         <v>268</v>
       </c>
       <c r="O77" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P77" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -11430,13 +11430,13 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
         <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -11448,16 +11448,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z77" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="AA77" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="AB77" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -11466,13 +11466,13 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH77" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AK77" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL77" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="AM77" t="n">
         <v>313</v>
@@ -11561,13 +11561,13 @@
         <v>333</v>
       </c>
       <c r="O78" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="P78" t="n">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="Q78" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -11585,25 +11585,25 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X78" t="n">
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="Z78" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="AA78" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="AB78" t="n">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="AC78" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -11621,16 +11621,16 @@
         <v>0</v>
       </c>
       <c r="AI78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AJ78" t="n">
         <v>0</v>
       </c>
       <c r="AK78" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AL78" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="AM78" t="n">
         <v>385</v>
@@ -11704,13 +11704,13 @@
         <v>292</v>
       </c>
       <c r="O79" t="n">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="P79" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R79" t="n">
         <v>1</v>
@@ -11728,25 +11728,25 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="X79" t="n">
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Z79" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="AA79" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AB79" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="AC79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD79" t="n">
         <v>1</v>
@@ -11764,16 +11764,16 @@
         <v>0</v>
       </c>
       <c r="AI79" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AJ79" t="n">
         <v>0</v>
       </c>
       <c r="AK79" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL79" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AM79" t="n">
         <v>419</v>
@@ -11847,13 +11847,13 @@
         <v>242</v>
       </c>
       <c r="O80" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P80" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="Q80" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -11871,25 +11871,25 @@
         <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="X80" t="n">
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="Z80" t="n">
+        <v>206</v>
+      </c>
+      <c r="AA80" t="n">
         <v>199</v>
       </c>
-      <c r="AA80" t="n">
-        <v>201</v>
-      </c>
       <c r="AB80" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AC80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11907,16 +11907,16 @@
         <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AJ80" t="n">
         <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AL80" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="AM80" t="n">
         <v>324</v>
@@ -11990,25 +11990,25 @@
         <v>233</v>
       </c>
       <c r="O81" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="P81" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="Q81" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="R81" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -12020,31 +12020,31 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="Z81" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="AA81" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="AB81" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="AC81" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AD81" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH81" t="n">
         <v>0</v>
@@ -12056,10 +12056,10 @@
         <v>0</v>
       </c>
       <c r="AK81" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AL81" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="AM81" t="n">
         <v>378</v>
@@ -12133,13 +12133,13 @@
         <v>335</v>
       </c>
       <c r="O82" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="P82" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="Q82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -12166,16 +12166,16 @@
         <v>383</v>
       </c>
       <c r="Z82" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="AA82" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AB82" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="AC82" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -12199,10 +12199,10 @@
         <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AL82" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="AM82" t="n">
         <v>367</v>
@@ -12276,16 +12276,16 @@
         <v>242</v>
       </c>
       <c r="O83" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="P83" t="n">
         <v>125</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S83" t="n">
         <v>12</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Z83" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="AA83" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="AB83" t="n">
         <v>125</v>
       </c>
       <c r="AC83" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AD83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE83" t="n">
         <v>12</v>
@@ -12342,10 +12342,10 @@
         <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AL83" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="AM83" t="n">
         <v>360</v>
@@ -12419,19 +12419,19 @@
         <v>259</v>
       </c>
       <c r="O84" t="n">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="P84" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="Q84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
         <v>0</v>
@@ -12449,25 +12449,25 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="Z84" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="AA84" t="n">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="AB84" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="AC84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF84" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AK84" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AL84" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="AM84" t="n">
         <v>356</v>
@@ -12565,13 +12565,13 @@
         <v>146</v>
       </c>
       <c r="P85" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -12595,19 +12595,19 @@
         <v>323</v>
       </c>
       <c r="Z85" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AA85" t="n">
         <v>146</v>
       </c>
       <c r="AB85" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -12631,7 +12631,7 @@
         <v>323</v>
       </c>
       <c r="AL85" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AM85" t="n">
         <v>301</v>
@@ -12705,13 +12705,13 @@
         <v>286</v>
       </c>
       <c r="O86" t="n">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="P86" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="Q86" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X86" t="n">
         <v>0</v>
@@ -12738,16 +12738,16 @@
         <v>420</v>
       </c>
       <c r="Z86" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="AA86" t="n">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="AB86" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="AC86" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -12765,7 +12765,7 @@
         <v>0</v>
       </c>
       <c r="AI86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ86" t="n">
         <v>0</v>
@@ -12774,7 +12774,7 @@
         <v>420</v>
       </c>
       <c r="AL86" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="AM86" t="n">
         <v>399</v>
@@ -12848,16 +12848,16 @@
         <v>251</v>
       </c>
       <c r="O87" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="P87" t="n">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="Q87" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -12872,28 +12872,28 @@
         <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X87" t="n">
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Z87" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AA87" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AB87" t="n">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="AC87" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -12908,16 +12908,16 @@
         <v>0</v>
       </c>
       <c r="AI87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AJ87" t="n">
         <v>0</v>
       </c>
       <c r="AK87" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AL87" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AM87" t="n">
         <v>366</v>
@@ -12991,20 +12991,20 @@
         <v>209</v>
       </c>
       <c r="O88" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="P88" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="Q88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R88" t="n">
+        <v>9</v>
+      </c>
+      <c r="S88" t="n">
         <v>6</v>
       </c>
-      <c r="S88" t="n">
-        <v>1</v>
-      </c>
       <c r="T88" t="n">
         <v>0</v>
       </c>
@@ -13015,32 +13015,32 @@
         <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X88" t="n">
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="Z88" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AA88" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AB88" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AC88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AD88" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE88" t="n">
         <v>6</v>
       </c>
-      <c r="AE88" t="n">
-        <v>1</v>
-      </c>
       <c r="AF88" t="n">
         <v>0</v>
       </c>
@@ -13051,16 +13051,16 @@
         <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ88" t="n">
         <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AL88" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AM88" t="n">
         <v>364</v>
@@ -13134,13 +13134,13 @@
         <v>360</v>
       </c>
       <c r="O89" t="n">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="P89" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -13158,25 +13158,25 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X89" t="n">
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="Z89" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="AA89" t="n">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="AB89" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AC89" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -13194,16 +13194,16 @@
         <v>0</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ89" t="n">
         <v>0</v>
       </c>
       <c r="AK89" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AL89" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="AM89" t="n">
         <v>440</v>
@@ -13277,13 +13277,13 @@
         <v>265</v>
       </c>
       <c r="O90" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P90" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="Q90" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -13301,7 +13301,7 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="X90" t="n">
         <v>0</v>
@@ -13310,16 +13310,16 @@
         <v>386</v>
       </c>
       <c r="Z90" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AA90" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AB90" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="AC90" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AI90" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AJ90" t="n">
         <v>0</v>
@@ -13346,7 +13346,7 @@
         <v>386</v>
       </c>
       <c r="AL90" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AM90" t="n">
         <v>335</v>
@@ -13420,76 +13420,76 @@
         <v>337</v>
       </c>
       <c r="O91" t="n">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="P91" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R91" t="n">
         <v>4</v>
       </c>
       <c r="S91" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="X91" t="n">
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="Z91" t="n">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="AA91" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB91" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="AC91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD91" t="n">
         <v>4</v>
       </c>
       <c r="AE91" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH91" t="n">
         <v>0</v>
       </c>
       <c r="AI91" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AJ91" t="n">
         <v>0</v>
       </c>
       <c r="AK91" t="n">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="AL91" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="AM91" t="n">
         <v>430</v>
@@ -13563,19 +13563,19 @@
         <v>215</v>
       </c>
       <c r="O92" t="n">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="P92" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="Q92" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" t="n">
         <v>0</v>
@@ -13593,25 +13593,25 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Z92" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="AA92" t="n">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="AB92" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AC92" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF92" t="n">
         <v>0</v>
@@ -13629,10 +13629,10 @@
         <v>0</v>
       </c>
       <c r="AK92" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AL92" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="AM92" t="n">
         <v>343</v>
@@ -13706,19 +13706,19 @@
         <v>380</v>
       </c>
       <c r="O93" t="n">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="P93" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="Q93" t="n">
         <v>2</v>
       </c>
       <c r="R93" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
         <v>0</v>
@@ -13736,25 +13736,25 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="Z93" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AA93" t="n">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="AB93" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="AC93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF93" t="n">
         <v>0</v>
@@ -13772,10 +13772,10 @@
         <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AL93" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AM93" t="n">
         <v>364</v>
@@ -13849,16 +13849,16 @@
         <v>385</v>
       </c>
       <c r="O94" t="n">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="P94" t="n">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="Q94" t="n">
         <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -13873,28 +13873,28 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y94" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Z94" t="n">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="AA94" t="n">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="AB94" t="n">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="AC94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD94" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -13909,16 +13909,16 @@
         <v>0</v>
       </c>
       <c r="AI94" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK94" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AL94" t="n">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="AM94" t="n">
         <v>437</v>
@@ -13992,19 +13992,19 @@
         <v>247</v>
       </c>
       <c r="O95" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="P95" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="Q95" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="R95" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S95" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T95" t="n">
         <v>0</v>
@@ -14022,25 +14022,25 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Z95" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="AA95" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="AB95" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="AC95" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AD95" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE95" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AF95" t="n">
         <v>0</v>
@@ -14058,10 +14058,10 @@
         <v>0</v>
       </c>
       <c r="AK95" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AL95" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="AM95" t="n">
         <v>472</v>
@@ -14135,19 +14135,19 @@
         <v>192</v>
       </c>
       <c r="O96" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="P96" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="Q96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T96" t="n">
         <v>0</v>
@@ -14165,25 +14165,25 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Z96" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="AA96" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AB96" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AC96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE96" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AF96" t="n">
         <v>0</v>
@@ -14201,10 +14201,10 @@
         <v>0</v>
       </c>
       <c r="AK96" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AL96" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="AM96" t="n">
         <v>340</v>
@@ -14278,16 +14278,16 @@
         <v>295</v>
       </c>
       <c r="O97" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="P97" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q97" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="R97" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -14302,28 +14302,28 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X97" t="n">
         <v>1</v>
       </c>
       <c r="Y97" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="Z97" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AA97" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AB97" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AC97" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AD97" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -14338,16 +14338,16 @@
         <v>0</v>
       </c>
       <c r="AI97" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ97" t="n">
         <v>1</v>
       </c>
       <c r="AK97" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="AL97" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AM97" t="n">
         <v>316</v>
@@ -14421,16 +14421,16 @@
         <v>387</v>
       </c>
       <c r="O98" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="P98" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Q98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -14454,19 +14454,19 @@
         <v>450</v>
       </c>
       <c r="Z98" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AA98" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AB98" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="AC98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE98" t="n">
         <v>5</v>
@@ -14490,7 +14490,7 @@
         <v>450</v>
       </c>
       <c r="AL98" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AM98" t="n">
         <v>422</v>
@@ -14564,10 +14564,10 @@
         <v>465</v>
       </c>
       <c r="O99" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P99" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="Q99" t="n">
         <v>3</v>
@@ -14576,7 +14576,7 @@
         <v>5</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
         <v>0</v>
@@ -14588,22 +14588,22 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="X99" t="n">
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Z99" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AA99" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB99" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AC99" t="n">
         <v>3</v>
@@ -14612,7 +14612,7 @@
         <v>5</v>
       </c>
       <c r="AE99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
         <v>0</v>
@@ -14624,16 +14624,16 @@
         <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AJ99" t="n">
         <v>0</v>
       </c>
       <c r="AK99" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL99" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AM99" t="n">
         <v>391</v>
@@ -14707,19 +14707,19 @@
         <v>250</v>
       </c>
       <c r="O100" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="P100" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="Q100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T100" t="n">
         <v>0</v>
@@ -14737,25 +14737,25 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="Z100" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="AA100" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AB100" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="AC100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AF100" t="n">
         <v>0</v>
@@ -14773,10 +14773,10 @@
         <v>0</v>
       </c>
       <c r="AK100" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AL100" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="AM100" t="n">
         <v>366</v>
@@ -14850,13 +14850,13 @@
         <v>243</v>
       </c>
       <c r="O101" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="P101" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="Q101" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -14874,25 +14874,25 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Z101" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="AA101" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="AB101" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="AC101" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AD101" t="n">
         <v>0</v>
@@ -14910,16 +14910,16 @@
         <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AJ101" t="n">
         <v>0</v>
       </c>
       <c r="AK101" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AL101" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="AM101" t="n">
         <v>335</v>
@@ -14993,22 +14993,22 @@
         <v>433</v>
       </c>
       <c r="O102" t="n">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="P102" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="Q102" t="n">
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -15017,34 +15017,34 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X102" t="n">
         <v>1</v>
       </c>
       <c r="Y102" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="Z102" t="n">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="AA102" t="n">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="AB102" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AC102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -15053,16 +15053,16 @@
         <v>0</v>
       </c>
       <c r="AI102" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AJ102" t="n">
         <v>1</v>
       </c>
       <c r="AK102" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="AL102" t="n">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="AM102" t="n">
         <v>398</v>
@@ -15136,19 +15136,19 @@
         <v>321</v>
       </c>
       <c r="O103" t="n">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="P103" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="Q103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
         <v>0</v>
@@ -15160,25 +15160,25 @@
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X103" t="n">
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Z103" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="AA103" t="n">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="AB103" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="AC103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD103" t="n">
         <v>0</v>
@@ -15196,16 +15196,16 @@
         <v>0</v>
       </c>
       <c r="AI103" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ103" t="n">
         <v>0</v>
       </c>
       <c r="AK103" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL103" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="AM103" t="n">
         <v>322</v>
@@ -15279,19 +15279,19 @@
         <v>322</v>
       </c>
       <c r="O104" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="P104" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
         <v>0</v>
@@ -15303,31 +15303,31 @@
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="X104" t="n">
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z104" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AA104" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AB104" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AC104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
         <v>0</v>
@@ -15339,16 +15339,16 @@
         <v>0</v>
       </c>
       <c r="AI104" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AJ104" t="n">
         <v>0</v>
       </c>
       <c r="AK104" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL104" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AM104" t="n">
         <v>288</v>
@@ -15422,13 +15422,13 @@
         <v>219</v>
       </c>
       <c r="O105" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="P105" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="Q105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R105" t="n">
         <v>2</v>
@@ -15452,19 +15452,19 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z105" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AA105" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AB105" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AC105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD105" t="n">
         <v>2</v>
@@ -15488,10 +15488,10 @@
         <v>0</v>
       </c>
       <c r="AK105" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AL105" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AM105" t="n">
         <v>294</v>
@@ -15565,13 +15565,13 @@
         <v>258</v>
       </c>
       <c r="O106" t="n">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="P106" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="Q106" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -15580,10 +15580,10 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V106" t="n">
         <v>0</v>
@@ -15598,16 +15598,16 @@
         <v>422</v>
       </c>
       <c r="Z106" t="n">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="AA106" t="n">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="AB106" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="AC106" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -15616,10 +15616,10 @@
         <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH106" t="n">
         <v>0</v>
@@ -15634,7 +15634,7 @@
         <v>422</v>
       </c>
       <c r="AL106" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="AM106" t="n">
         <v>403</v>
@@ -15708,16 +15708,16 @@
         <v>490</v>
       </c>
       <c r="O107" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P107" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S107" t="n">
         <v>1</v>
@@ -15732,7 +15732,7 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="X107" t="n">
         <v>0</v>
@@ -15741,19 +15741,19 @@
         <v>481</v>
       </c>
       <c r="Z107" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA107" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB107" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AC107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD107" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -15768,7 +15768,7 @@
         <v>0</v>
       </c>
       <c r="AI107" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AJ107" t="n">
         <v>0</v>
@@ -15777,7 +15777,7 @@
         <v>481</v>
       </c>
       <c r="AL107" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM107" t="n">
         <v>432</v>
@@ -15851,19 +15851,19 @@
         <v>342</v>
       </c>
       <c r="O108" t="n">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="P108" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="Q108" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T108" t="n">
         <v>0</v>
@@ -15881,25 +15881,25 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Z108" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="AA108" t="n">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="AB108" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="AC108" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF108" t="n">
         <v>0</v>
@@ -15917,10 +15917,10 @@
         <v>0</v>
       </c>
       <c r="AK108" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AL108" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="AM108" t="n">
         <v>362</v>
@@ -15994,13 +15994,13 @@
         <v>574</v>
       </c>
       <c r="O109" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="P109" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -16024,19 +16024,19 @@
         <v>4</v>
       </c>
       <c r="Y109" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="Z109" t="n">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="AA109" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="AB109" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
@@ -16060,10 +16060,10 @@
         <v>4</v>
       </c>
       <c r="AK109" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="AL109" t="n">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="AM109" t="n">
         <v>412</v>
@@ -16280,16 +16280,16 @@
         <v>316</v>
       </c>
       <c r="O111" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="P111" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="Q111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -16310,22 +16310,22 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="Z111" t="n">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="AA111" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="AB111" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="AC111" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE111" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AK111" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AL111" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="AM111" t="n">
         <v>255</v>
@@ -16423,19 +16423,19 @@
         <v>695</v>
       </c>
       <c r="O112" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="P112" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="Q112" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T112" t="n">
         <v>0</v>
@@ -16447,31 +16447,31 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="X112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y112" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="Z112" t="n">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="AA112" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AB112" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AC112" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF112" t="n">
         <v>0</v>
@@ -16483,16 +16483,16 @@
         <v>0</v>
       </c>
       <c r="AI112" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AJ112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK112" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="AL112" t="n">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="AM112" t="n">
         <v>382</v>
@@ -16566,19 +16566,19 @@
         <v>226</v>
       </c>
       <c r="O113" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="P113" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
         <v>0</v>
@@ -16596,25 +16596,25 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="Z113" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AA113" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="AB113" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
         <v>0</v>
@@ -16632,10 +16632,10 @@
         <v>0</v>
       </c>
       <c r="AK113" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AL113" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AM113" t="n">
         <v>420</v>
@@ -16709,19 +16709,19 @@
         <v>240</v>
       </c>
       <c r="O114" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="P114" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="Q114" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T114" t="n">
         <v>0</v>
@@ -16739,25 +16739,25 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Z114" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="AA114" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AB114" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="AC114" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF114" t="n">
         <v>0</v>
@@ -16775,10 +16775,10 @@
         <v>0</v>
       </c>
       <c r="AK114" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AL114" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="AM114" t="n">
         <v>333</v>
@@ -16852,19 +16852,19 @@
         <v>251</v>
       </c>
       <c r="O115" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="P115" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="Q115" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T115" t="n">
         <v>0</v>
@@ -16885,22 +16885,22 @@
         <v>417</v>
       </c>
       <c r="Z115" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="AA115" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="AB115" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="AC115" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF115" t="n">
         <v>0</v>
@@ -16921,7 +16921,7 @@
         <v>417</v>
       </c>
       <c r="AL115" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="AM115" t="n">
         <v>364</v>
@@ -16995,19 +16995,19 @@
         <v>321</v>
       </c>
       <c r="O116" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="P116" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="Q116" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T116" t="n">
         <v>0</v>
@@ -17019,34 +17019,34 @@
         <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="Z116" t="n">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="AA116" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AB116" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="AC116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
       </c>
       <c r="AF116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -17055,16 +17055,16 @@
         <v>0</v>
       </c>
       <c r="AI116" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AJ116" t="n">
         <v>0</v>
       </c>
       <c r="AK116" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="AL116" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AM116" t="n">
         <v>378</v>
@@ -17138,13 +17138,13 @@
         <v>492</v>
       </c>
       <c r="O117" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="P117" t="n">
         <v>178</v>
       </c>
       <c r="Q117" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
@@ -17171,16 +17171,16 @@
         <v>462</v>
       </c>
       <c r="Z117" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AA117" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="AB117" t="n">
         <v>178</v>
       </c>
       <c r="AC117" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -17207,7 +17207,7 @@
         <v>462</v>
       </c>
       <c r="AL117" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AM117" t="n">
         <v>420</v>
@@ -17281,16 +17281,16 @@
         <v>255</v>
       </c>
       <c r="O118" t="n">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="P118" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="Q118" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="R118" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S118" t="n">
         <v>1</v>
@@ -17311,25 +17311,25 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="Z118" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="AA118" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AB118" t="n">
         <v>138</v>
       </c>
       <c r="AC118" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="AD118" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE118" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AF118" t="n">
         <v>0</v>
@@ -17347,10 +17347,10 @@
         <v>0</v>
       </c>
       <c r="AK118" t="n">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="AL118" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="AM118" t="n">
         <v>336</v>
@@ -17424,13 +17424,13 @@
         <v>237</v>
       </c>
       <c r="O119" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P119" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="Q119" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
@@ -17454,19 +17454,19 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Z119" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AA119" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AB119" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="AC119" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -17490,10 +17490,10 @@
         <v>0</v>
       </c>
       <c r="AK119" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AL119" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM119" t="n">
         <v>344</v>
@@ -17567,19 +17567,19 @@
         <v>519</v>
       </c>
       <c r="O120" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="P120" t="n">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="Q120" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
         <v>0</v>
@@ -17591,31 +17591,31 @@
         <v>0</v>
       </c>
       <c r="W120" t="n">
+        <v>15</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>364</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>137</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>341</v>
+      </c>
+      <c r="AC120" t="n">
         <v>7</v>
       </c>
-      <c r="X120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>488</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>344</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>144</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>318</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>18</v>
-      </c>
       <c r="AD120" t="n">
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
         <v>0</v>
@@ -17627,16 +17627,16 @@
         <v>0</v>
       </c>
       <c r="AI120" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AJ120" t="n">
         <v>0</v>
       </c>
       <c r="AK120" t="n">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="AL120" t="n">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="AM120" t="n">
         <v>353</v>
@@ -17710,13 +17710,13 @@
         <v>288</v>
       </c>
       <c r="O121" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="P121" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="Q121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
@@ -17740,19 +17740,19 @@
         <v>1</v>
       </c>
       <c r="Y121" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Z121" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="AA121" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AB121" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="AC121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -17776,10 +17776,10 @@
         <v>1</v>
       </c>
       <c r="AK121" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AL121" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="AM121" t="n">
         <v>321</v>
@@ -17853,13 +17853,13 @@
         <v>164</v>
       </c>
       <c r="O122" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="P122" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="Q122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
         <v>0</v>
@@ -17883,16 +17883,16 @@
         <v>1</v>
       </c>
       <c r="Y122" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="Z122" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="AA122" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="AB122" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -17919,10 +17919,10 @@
         <v>1</v>
       </c>
       <c r="AK122" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="AL122" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="AM122" t="n">
         <v>297</v>
@@ -17996,19 +17996,19 @@
         <v>273</v>
       </c>
       <c r="O123" t="n">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="P123" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="Q123" t="n">
         <v>4</v>
       </c>
       <c r="R123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S123" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="T123" t="n">
         <v>0</v>
@@ -18026,25 +18026,25 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="Z123" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="AA123" t="n">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="AB123" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="AC123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE123" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="AF123" t="n">
         <v>0</v>
@@ -18062,10 +18062,10 @@
         <v>0</v>
       </c>
       <c r="AK123" t="n">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="AL123" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="AM123" t="n">
         <v>367</v>
@@ -18139,16 +18139,16 @@
         <v>405</v>
       </c>
       <c r="O124" t="n">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="P124" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="Q124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R124" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -18169,22 +18169,22 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="Z124" t="n">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="AA124" t="n">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="AB124" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="AC124" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD124" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -18205,10 +18205,10 @@
         <v>0</v>
       </c>
       <c r="AK124" t="n">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="AL124" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="AM124" t="n">
         <v>410</v>
@@ -18282,22 +18282,22 @@
         <v>341</v>
       </c>
       <c r="O125" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="P125" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="S125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -18306,34 +18306,34 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X125" t="n">
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="Z125" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="AA125" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AB125" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -18342,16 +18342,16 @@
         <v>0</v>
       </c>
       <c r="AI125" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AJ125" t="n">
         <v>0</v>
       </c>
       <c r="AK125" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="AL125" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="AM125" t="n">
         <v>394</v>
@@ -18425,13 +18425,13 @@
         <v>364</v>
       </c>
       <c r="O126" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="P126" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="Q126" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
@@ -18455,19 +18455,19 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z126" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="AA126" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="AB126" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="AC126" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -18491,10 +18491,10 @@
         <v>0</v>
       </c>
       <c r="AK126" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL126" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="AM126" t="n">
         <v>324</v>
@@ -18568,19 +18568,19 @@
         <v>310</v>
       </c>
       <c r="O127" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="P127" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="Q127" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T127" t="n">
         <v>0</v>
@@ -18598,25 +18598,25 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="Z127" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="AA127" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AB127" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="AC127" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF127" t="n">
         <v>0</v>
@@ -18634,10 +18634,10 @@
         <v>0</v>
       </c>
       <c r="AK127" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AL127" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="AM127" t="n">
         <v>384</v>
@@ -18711,50 +18711,50 @@
         <v>330</v>
       </c>
       <c r="O128" t="n">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="P128" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="Q128" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
       <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>17</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>494</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>261</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>233</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>236</v>
+      </c>
+      <c r="AC128" t="n">
         <v>8</v>
       </c>
-      <c r="T128" t="n">
-        <v>9</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>492</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>240</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>246</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>240</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>7</v>
-      </c>
       <c r="AD128" t="n">
         <v>0</v>
       </c>
@@ -18771,16 +18771,16 @@
         <v>0</v>
       </c>
       <c r="AI128" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AJ128" t="n">
         <v>0</v>
       </c>
       <c r="AK128" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL128" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="AM128" t="n">
         <v>457</v>
@@ -18854,17 +18854,17 @@
         <v>410</v>
       </c>
       <c r="O129" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="P129" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="Q129" t="n">
+        <v>4</v>
+      </c>
+      <c r="R129" t="n">
         <v>7</v>
       </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
       <c r="S129" t="n">
         <v>0</v>
       </c>
@@ -18878,28 +18878,28 @@
         <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="X129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="Z129" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="AA129" t="n">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="AB129" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="AC129" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -18914,16 +18914,16 @@
         <v>0</v>
       </c>
       <c r="AI129" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AJ129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK129" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="AL129" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="AM129" t="n">
         <v>429</v>
@@ -18997,13 +18997,13 @@
         <v>427</v>
       </c>
       <c r="O130" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="P130" t="n">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="Q130" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -19027,19 +19027,19 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="Z130" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="AA130" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="AB130" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -19063,10 +19063,10 @@
         <v>0</v>
       </c>
       <c r="AK130" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AL130" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="AM130" t="n">
         <v>313</v>
@@ -19140,19 +19140,19 @@
         <v>265</v>
       </c>
       <c r="O131" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="P131" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="Q131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R131" t="n">
         <v>1</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
         <v>0</v>
@@ -19170,16 +19170,16 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="Z131" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="AA131" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AB131" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -19188,7 +19188,7 @@
         <v>1</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF131" t="n">
         <v>0</v>
@@ -19206,10 +19206,10 @@
         <v>0</v>
       </c>
       <c r="AK131" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AL131" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="AM131" t="n">
         <v>324</v>
@@ -19283,19 +19283,19 @@
         <v>226</v>
       </c>
       <c r="O132" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="P132" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="Q132" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="R132" t="n">
         <v>2</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T132" t="n">
         <v>0</v>
@@ -19313,25 +19313,25 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z132" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="AA132" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AB132" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="AC132" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AD132" t="n">
         <v>2</v>
       </c>
       <c r="AE132" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AF132" t="n">
         <v>0</v>
@@ -19349,10 +19349,10 @@
         <v>0</v>
       </c>
       <c r="AK132" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL132" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="AM132" t="n">
         <v>377</v>
@@ -19426,16 +19426,16 @@
         <v>272</v>
       </c>
       <c r="O133" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="P133" t="n">
         <v>163</v>
       </c>
       <c r="Q133" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="R133" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -19456,22 +19456,22 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z133" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="AA133" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="AB133" t="n">
         <v>163</v>
       </c>
       <c r="AC133" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="AD133" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -19492,10 +19492,10 @@
         <v>0</v>
       </c>
       <c r="AK133" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL133" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="AM133" t="n">
         <v>386</v>
@@ -19569,16 +19569,16 @@
         <v>328</v>
       </c>
       <c r="O134" t="n">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="P134" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="Q134" t="n">
+        <v>1</v>
+      </c>
+      <c r="R134" t="n">
         <v>5</v>
-      </c>
-      <c r="R134" t="n">
-        <v>1</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -19602,19 +19602,19 @@
         <v>398</v>
       </c>
       <c r="Z134" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="AA134" t="n">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="AB134" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="AC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD134" t="n">
         <v>5</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>1</v>
       </c>
       <c r="AE134" t="n">
         <v>0</v>
@@ -19638,7 +19638,7 @@
         <v>398</v>
       </c>
       <c r="AL134" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="AM134" t="n">
         <v>370</v>
@@ -19712,31 +19712,31 @@
         <v>230</v>
       </c>
       <c r="O135" t="n">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="P135" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="Q135" t="n">
+        <v>11</v>
+      </c>
+      <c r="R135" t="n">
+        <v>1</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
         <v>12</v>
-      </c>
-      <c r="R135" t="n">
-        <v>2</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>5</v>
       </c>
       <c r="X135" t="n">
         <v>0</v>
@@ -19745,19 +19745,19 @@
         <v>414</v>
       </c>
       <c r="Z135" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="AA135" t="n">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="AB135" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="AC135" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AD135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE135" t="n">
         <v>0</v>
@@ -19781,7 +19781,7 @@
         <v>414</v>
       </c>
       <c r="AL135" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="AM135" t="n">
         <v>368</v>
